--- a/data/trans_dic/P55$amigo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,96</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,16</t>
+          <t>1,07; 6,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,39</t>
+          <t>0,47; 4,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,41</t>
+          <t>0,4; 3,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,42</t>
+          <t>1,13; 5,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,47</t>
+          <t>3,23; 7,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,49</t>
+          <t>0,56; 3,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,87</t>
+          <t>0,29; 2,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,56</t>
+          <t>0,81; 4,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,47</t>
+          <t>3,05; 6,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,65</t>
+          <t>0,0; 24,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,22</t>
+          <t>0,0; 51,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 18,31</t>
+          <t>3,17; 18,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,12</t>
+          <t>0,93; 8,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,84</t>
+          <t>0,0; 14,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,57</t>
+          <t>0,0; 28,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 10,23</t>
+          <t>2,93; 10,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,97</t>
+          <t>0,0; 28,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,31</t>
+          <t>0,0; 43,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 28,58</t>
+          <t>3,31; 29,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,71</t>
+          <t>0,0; 29,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 19,1</t>
+          <t>2,04; 20,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,12</t>
+          <t>0,71; 9,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,59</t>
+          <t>2,72; 8,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,04</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,83</t>
+          <t>0,36; 3,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,88</t>
+          <t>0,93; 5,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,03</t>
+          <t>3,42; 6,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,18</t>
+          <t>1,0; 3,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,87</t>
+          <t>0,74; 3,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,21</t>
+          <t>0,84; 4,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,56</t>
+          <t>3,68; 6,66</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5112</t>
+          <t>0; 5028</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>0; 5346</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4653</t>
+          <t>0; 5939</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1142; 6995</t>
+          <t>1048; 6635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>941; 9041</t>
+          <t>960; 9809</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>993; 8564</t>
+          <t>992; 8775</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2381; 13382</t>
+          <t>2359; 12131</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8550; 19250</t>
+          <t>8323; 19278</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1675; 10782</t>
+          <t>1738; 9947</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1078; 10749</t>
+          <t>1095; 9780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2431; 13775</t>
+          <t>2445; 13985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10675; 22979</t>
+          <t>10836; 23361</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4207</t>
+          <t>0; 3438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9651</t>
+          <t>0; 10344</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1614</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1545; 7878</t>
+          <t>1363; 7799</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2113</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5952</t>
+          <t>0; 4978</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>497; 4439</t>
+          <t>508; 4588</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3554</t>
+          <t>0; 3996</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 11760</t>
+          <t>0; 11652</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5871</t>
+          <t>0; 5887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2973; 9989</t>
+          <t>2858; 10509</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2177</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1154</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4531</t>
+          <t>0; 4243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5822</t>
+          <t>0; 5017</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>453; 3998</t>
+          <t>462; 4101</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5592</t>
+          <t>0; 6108</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1704</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>586; 5559</t>
+          <t>593; 5945</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6085</t>
+          <t>0; 6390</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1056; 14792</t>
+          <t>1039; 14098</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 6211</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3911; 13376</t>
+          <t>4245; 13235</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2104; 11637</t>
+          <t>2066; 11894</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>986; 7835</t>
+          <t>987; 9486</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3454; 15713</t>
+          <t>2478; 15565</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11210; 22942</t>
+          <t>11155; 22817</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3620; 14944</t>
+          <t>3573; 13827</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3035; 16357</t>
+          <t>3142; 16528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3582; 16351</t>
+          <t>3260; 15803</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17354; 31627</t>
+          <t>17763; 32123</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$amigo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,35</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,79</t>
+          <t>0,97; 6,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,77</t>
+          <t>0,56; 4,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,5</t>
+          <t>0,4; 3,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,82</t>
+          <t>1,14; 6,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,48</t>
+          <t>3,36; 8,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,22</t>
+          <t>0,54; 3,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,61</t>
+          <t>0,28; 2,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,63</t>
+          <t>0,82; 4,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,57</t>
+          <t>3,13; 6,6</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,23</t>
+          <t>0,0; 29,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,68</t>
+          <t>0,0; 48,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 18,13</t>
+          <t>3,15; 15,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,57</t>
+          <t>0,0; 11,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,39</t>
+          <t>0,82; 8,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,43</t>
+          <t>0,0; 14,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,3</t>
+          <t>0,0; 25,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 10,76</t>
+          <t>2,63; 9,27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,06</t>
+          <t>0,0; 26,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,36</t>
+          <t>0,0; 45,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 29,32</t>
+          <t>3,05; 29,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,18</t>
+          <t>0,0; 29,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 20,43</t>
+          <t>2,8; 20,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,64</t>
+          <t>0,71; 9,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,5</t>
+          <t>2,39; 7,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,91; 5,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,43</t>
+          <t>0,36; 3,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,82</t>
+          <t>0,92; 5,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,99</t>
+          <t>3,4; 7,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,87</t>
+          <t>0,91; 3,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,91</t>
+          <t>0,76; 4,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,06</t>
+          <t>0,92; 4,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,66</t>
+          <t>3,57; 6,74</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>17484</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5028</t>
+          <t>0; 5018</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5346</t>
+          <t>0; 5714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5939</t>
+          <t>0; 5007</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1048; 6635</t>
+          <t>1002; 6888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>960; 9809</t>
+          <t>1159; 9707</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>992; 8775</t>
+          <t>994; 8588</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2359; 12131</t>
+          <t>2383; 13444</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8323; 19278</t>
+          <t>9312; 22235</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1738; 9947</t>
+          <t>1657; 10726</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1095; 9780</t>
+          <t>1066; 9905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2445; 13985</t>
+          <t>2467; 13982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10836; 23361</t>
+          <t>11897; 25100</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5619</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3438</t>
+          <t>0; 4255</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 10344</t>
+          <t>0; 9731</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1363; 7799</t>
+          <t>1492; 7303</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4978</t>
+          <t>0; 5934</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>508; 4588</t>
+          <t>512; 5039</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3996</t>
+          <t>0; 3971</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 11652</t>
+          <t>0; 10695</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5887</t>
+          <t>0; 6455</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2858; 10509</t>
+          <t>2896; 10197</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2669</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4243</t>
+          <t>0; 4461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5017</t>
+          <t>0; 5259</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>462; 4101</t>
+          <t>481; 4580</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6108</t>
+          <t>0; 6095</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>593; 5945</t>
+          <t>905; 6465</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>25771</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6390</t>
+          <t>0; 5643</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1039; 14098</t>
+          <t>1040; 13502</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6211</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4245; 13235</t>
+          <t>4008; 12867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2066; 11894</t>
+          <t>2095; 11614</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>987; 9486</t>
+          <t>995; 8816</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2478; 15565</t>
+          <t>2472; 14437</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11155; 22817</t>
+          <t>12063; 25760</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3573; 13827</t>
+          <t>3256; 14253</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3142; 16528</t>
+          <t>3230; 18282</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3260; 15803</t>
+          <t>3582; 16601</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17763; 32123</t>
+          <t>18647; 35259</t>
         </is>
       </c>
     </row>
